--- a/public/exports/29189897.xlsx
+++ b/public/exports/29189897.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100643290</t>
+          <t xml:space="preserve">100193487, 100193488</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F2">
-        <v>1165</v>
+        <v>6126</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080895</t>
+          <t xml:space="preserve">100643290</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F3">
-        <v>376</v>
+        <v>1165</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100992519</t>
+          <t xml:space="preserve">10080895</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10100782</t>
+          <t xml:space="preserve">100891244, 100891245</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F5">
-        <v>4712</v>
+        <v>5997</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4385440</t>
+          <t xml:space="preserve">100992519</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>265</v>
+        <v>400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387965</t>
+          <t xml:space="preserve">10100782</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F7">
-        <v>1061</v>
+        <v>4712</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">304880, 304881</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>1172</v>
+        <v>2656</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">314810</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F9">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5026732</t>
+          <t xml:space="preserve">315765</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>535</v>
+        <v>355</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5030285</t>
+          <t xml:space="preserve">320227</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>880</v>
+        <v>1264</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065053</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F12">
-        <v>733</v>
+        <v>1190</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067709, 100756343</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F13">
-        <v>1142</v>
+        <v>421</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F14">
-        <v>1473</v>
+        <v>421</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F15">
-        <v>1247</v>
+        <v>443</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F16">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F17">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">320228</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F18">
-        <v>539</v>
+        <v>1190</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">320650, 320651, 320652</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>409</v>
+        <v>2140</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">322724, 322725</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>431</v>
+        <v>1159</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">323176, 323177, 323178</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>468</v>
+        <v>4203</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5676543</t>
+          <t xml:space="preserve">4385440</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F22">
-        <v>750</v>
+        <v>265</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677319</t>
+          <t xml:space="preserve">4387965</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F23">
-        <v>745</v>
+        <v>1061</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677324</t>
+          <t xml:space="preserve">5026732</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F24">
-        <v>1343</v>
+        <v>535</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677324</t>
+          <t xml:space="preserve">5030285</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>968</v>
+        <v>880</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5678022</t>
+          <t xml:space="preserve">5067709, 100756343</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F26">
-        <v>1555</v>
+        <v>1142</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5680207</t>
+          <t xml:space="preserve">5676543</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>990</v>
+        <v>750</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5683897</t>
+          <t xml:space="preserve">5677319</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F28">
-        <v>442</v>
+        <v>745</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5683897</t>
+          <t xml:space="preserve">5678022</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>272</v>
+        <v>1555</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5686174</t>
+          <t xml:space="preserve">5680207</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F30">
-        <v>512</v>
+        <v>990</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766687</t>
+          <t xml:space="preserve">5686174</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F31">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">738521, 8963331</t>
+          <t xml:space="preserve">738541, 5681084</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>1873</v>
+        <v>905</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">738541, 5681084</t>
+          <t xml:space="preserve">738573, 5687221</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F33">
-        <v>905</v>
+        <v>484</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">738542, 5063543</t>
+          <t xml:space="preserve">738574, 5687221</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>2158</v>
+        <v>352</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">738545, 4386252</t>
+          <t xml:space="preserve">738581, 4383225</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>314</v>
+        <v>4629</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">738545, 4386252</t>
+          <t xml:space="preserve">738581, 4383225</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F36">
-        <v>1647</v>
+        <v>1333</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">738573, 5687221</t>
+          <t xml:space="preserve">738581, 4383225</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F37">
-        <v>484</v>
+        <v>1578</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">738574, 5687221</t>
+          <t xml:space="preserve">738581, 4383225</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F38">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">738581, 4383225</t>
+          <t xml:space="preserve">738659, 5682839</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F39">
-        <v>4629</v>
+        <v>1108</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">738581, 4383225</t>
+          <t xml:space="preserve">738731, 5023176</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F40">
-        <v>1333</v>
+        <v>1844</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">738581, 4383225</t>
+          <t xml:space="preserve">738771, 5169632</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>1578</v>
+        <v>484</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">738581, 4383225</t>
+          <t xml:space="preserve">738771, 5169632</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F42">
-        <v>470</v>
+        <v>1456</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">738659, 5682839</t>
+          <t xml:space="preserve">738775, 5066251</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F43">
-        <v>1108</v>
+        <v>997</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">738731, 5023176</t>
+          <t xml:space="preserve">738780, 7900558</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F44">
-        <v>1844</v>
+        <v>320</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">738733, 7110243</t>
+          <t xml:space="preserve">7885692</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>7097</v>
+        <v>461</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">738771, 5169632</t>
+          <t xml:space="preserve">8211974</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F46">
-        <v>484</v>
+        <v>1374</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">738771, 5169632</t>
+          <t xml:space="preserve">8761494</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F47">
-        <v>1456</v>
+        <v>405</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">738775, 5066251</t>
+          <t xml:space="preserve">9072750</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F48">
-        <v>997</v>
+        <v>960</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">738780, 7900558</t>
+          <t xml:space="preserve">9072750</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F49">
-        <v>320</v>
+        <v>676</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251, 100756360</t>
+          <t xml:space="preserve">9072750</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F50">
-        <v>1749</v>
+        <v>1138</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885692</t>
+          <t xml:space="preserve">9072750</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F51">
-        <v>461</v>
+        <v>1186</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211974</t>
+          <t xml:space="preserve">9072750</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F52">
-        <v>1374</v>
+        <v>480</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761494</t>
+          <t xml:space="preserve">9072750</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F53">
-        <v>405</v>
+        <v>808</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072750</t>
+          <t xml:space="preserve">9413750</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F54">
-        <v>960</v>
+        <v>343</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072750</t>
+          <t xml:space="preserve">9925506</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F55">
-        <v>676</v>
+        <v>1890</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072750</t>
+          <t xml:space="preserve">9925506</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F56">
-        <v>1138</v>
+        <v>561</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>1186</v>
+        <v>1964</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025100</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-08</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2881,30 +2881,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072750</t>
+          <t xml:space="preserve">738542, 5063543</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>480</v>
+        <v>2158</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056887</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-01-24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2931,30 +2931,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072750</t>
+          <t xml:space="preserve">5676212</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>808</v>
+        <v>382</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311089253</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-12-22</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413750</t>
+          <t xml:space="preserve">738545, 4386252</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311094238</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-05</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3031,30 +3031,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9925506</t>
+          <t xml:space="preserve">738545, 4386252</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>1890</v>
+        <v>1647</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311094238</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-05</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3081,30 +3081,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9925506</t>
+          <t xml:space="preserve">5675704</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>561</v>
+        <v>1674</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311144283</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677324</t>
+          <t xml:space="preserve">5675704</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F63">
-        <v>415</v>
+        <v>885</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022764</t>
+          <t xml:space="preserve">311144284</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-25</t>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072750</t>
+          <t xml:space="preserve">5675704</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F64">
-        <v>1964</v>
+        <v>441</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025100</t>
+          <t xml:space="preserve">311144285</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-08</t>
+          <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">10170544</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>732</v>
+        <v>2304</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026411</t>
+          <t xml:space="preserve">311149262</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-06</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963331</t>
+          <t xml:space="preserve">5766687</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>2958</v>
+        <v>520</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051450</t>
+          <t xml:space="preserve">311154376</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-07-19</t>
+          <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5676212</t>
+          <t xml:space="preserve">5681894</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>382</v>
+        <v>928</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089253</t>
+          <t xml:space="preserve">311156884</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-22</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675704</t>
+          <t xml:space="preserve">5681894</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F68">
-        <v>1674</v>
+        <v>745</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144283</t>
+          <t xml:space="preserve">311156886</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675704</t>
+          <t xml:space="preserve">5681894</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F69">
-        <v>885</v>
+        <v>802</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144284</t>
+          <t xml:space="preserve">311156886</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675704</t>
+          <t xml:space="preserve">4387740</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311144285</t>
+          <t xml:space="preserve">311157144</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-09</t>
+          <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">10170544</t>
+          <t xml:space="preserve">4387740</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F71">
-        <v>2304</v>
+        <v>360</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149262</t>
+          <t xml:space="preserve">311157144</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681894</t>
+          <t xml:space="preserve">4387740</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F72">
-        <v>928</v>
+        <v>565</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156884</t>
+          <t xml:space="preserve">311157144</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681894</t>
+          <t xml:space="preserve">4387740</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F73">
-        <v>745</v>
+        <v>407</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156886</t>
+          <t xml:space="preserve">311157144</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681894</t>
+          <t xml:space="preserve">9292774</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>802</v>
+        <v>256</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156886</t>
+          <t xml:space="preserve">311162342</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2026-03-03</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387740</t>
+          <t xml:space="preserve">4386732</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>372</v>
+        <v>976</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311157144</t>
+          <t xml:space="preserve">311167181</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-04</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387740</t>
+          <t xml:space="preserve">4386732</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F76">
-        <v>360</v>
+        <v>597</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311157144</t>
+          <t xml:space="preserve">311167181</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-04</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387740</t>
+          <t xml:space="preserve">4386732</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>565</v>
+        <v>390</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311157144</t>
+          <t xml:space="preserve">311167181</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-04</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387740</t>
+          <t xml:space="preserve">4386732</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F78">
-        <v>407</v>
+        <v>1281</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311157144</t>
+          <t xml:space="preserve">311167181</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-04</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9292774</t>
+          <t xml:space="preserve">4386732</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F79">
-        <v>256</v>
+        <v>441</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162342</t>
+          <t xml:space="preserve">311167181</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-03</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">320227</t>
+          <t xml:space="preserve">5029065</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>1264</v>
+        <v>496</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164294</t>
+          <t xml:space="preserve">311167182</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">8211974</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>1190</v>
+        <v>7651</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311174659</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">5068289</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F82">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311180650</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-06-02</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">5677649</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,16 +4140,16 @@
         </is>
       </c>
       <c r="F83">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311193661</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,35 +4181,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">4387471</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311207510</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">5687121</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311207659</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4281,35 +4281,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">5067709</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>421</v>
+        <v>711</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311210849</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4331,35 +4331,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">320228</t>
+          <t xml:space="preserve">5067709</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F87">
-        <v>1190</v>
+        <v>421</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311164293</t>
+          <t xml:space="preserve">311210849</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386732</t>
+          <t xml:space="preserve">5677319</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,26 +4390,26 @@
         </is>
       </c>
       <c r="F88">
-        <v>976</v>
+        <v>446</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311167181</t>
+          <t xml:space="preserve">311210804</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4431,35 +4431,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386732</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F89">
-        <v>597</v>
+        <v>1835</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311167181</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386732</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,26 +4490,26 @@
         </is>
       </c>
       <c r="F90">
-        <v>390</v>
+        <v>1210</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311167181</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386732</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,26 +4540,26 @@
         </is>
       </c>
       <c r="F91">
-        <v>1281</v>
+        <v>755</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311167181</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4581,35 +4581,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386732</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F92">
-        <v>441</v>
+        <v>1102</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311167181</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4631,35 +4631,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5029065</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F93">
-        <v>496</v>
+        <v>846</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311167182</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4681,35 +4681,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8211974</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F94">
-        <v>7651</v>
+        <v>932</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311174659</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4731,35 +4731,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5068289</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F95">
-        <v>438</v>
+        <v>732</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311180650</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4781,35 +4781,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677649</t>
+          <t xml:space="preserve">7885662</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F96">
-        <v>470</v>
+        <v>1668</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311193661</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-09</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387471</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,16 +4840,16 @@
         </is>
       </c>
       <c r="F97">
-        <v>484</v>
+        <v>1133</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207510</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5687121</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F98">
-        <v>442</v>
+        <v>669</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207659</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067709</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F99">
-        <v>711</v>
+        <v>1037</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210849</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067709</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F100">
-        <v>421</v>
+        <v>1019</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210849</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677319</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F101">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210804</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F102">
-        <v>1835</v>
+        <v>655</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F103">
-        <v>1210</v>
+        <v>458</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F104">
-        <v>755</v>
+        <v>1982</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212891</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F105">
-        <v>1102</v>
+        <v>461</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212891</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F106">
-        <v>846</v>
+        <v>802</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F107">
-        <v>932</v>
+        <v>960</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7885662</t>
+          <t xml:space="preserve">4389038</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F108">
-        <v>1668</v>
+        <v>660</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311212893</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5436,11 +5436,11 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F109">
-        <v>1133</v>
+        <v>288</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5486,11 +5486,11 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F110">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5536,11 +5536,11 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F111">
-        <v>1037</v>
+        <v>655</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">100022289</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>1019</v>
+        <v>2634</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311214377</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5675351</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>496</v>
+        <v>6258</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311218564</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">4382695</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
-        <v>655</v>
+        <v>321</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311215688</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5066243</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>458</v>
+        <v>1010</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311226576</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5675287</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F116">
-        <v>1982</v>
+        <v>1211</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212891</t>
+          <t xml:space="preserve">311226584</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5675287</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F117">
-        <v>461</v>
+        <v>830</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212891</t>
+          <t xml:space="preserve">311226584</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5675287</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F118">
-        <v>802</v>
+        <v>1155</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311226584</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5683897</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F119">
-        <v>960</v>
+        <v>442</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311226587</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5683897</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="F120">
-        <v>660</v>
+        <v>272</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311226587</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">8922221</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121">
-        <v>288</v>
+        <v>1075</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311226585</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5681221</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F122">
-        <v>638</v>
+        <v>2283</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311226923</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-07</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4389038</t>
+          <t xml:space="preserve">5066243</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>655</v>
+        <v>731</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212893</t>
+          <t xml:space="preserve">311227488</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100022289</t>
+          <t xml:space="preserve">5677321</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>2634</v>
+        <v>660</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214377</t>
+          <t xml:space="preserve">311227481</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675351</t>
+          <t xml:space="preserve">5677649</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>6258</v>
+        <v>832</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218564</t>
+          <t xml:space="preserve">311227482</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382695</t>
+          <t xml:space="preserve">5682777</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215688</t>
+          <t xml:space="preserve">311227491</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5066243</t>
+          <t xml:space="preserve">5682777</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>1010</v>
+        <v>410</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226576</t>
+          <t xml:space="preserve">311227491</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675287</t>
+          <t xml:space="preserve">5682777</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F128">
-        <v>1211</v>
+        <v>401</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226584</t>
+          <t xml:space="preserve">311227491</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675287</t>
+          <t xml:space="preserve">5682777</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="F129">
-        <v>830</v>
+        <v>585</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226584</t>
+          <t xml:space="preserve">311227491</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675287</t>
+          <t xml:space="preserve">5681107</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>1155</v>
+        <v>1471</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226584</t>
+          <t xml:space="preserve">311230458</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677324</t>
+          <t xml:space="preserve">5068289</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>1105</v>
+        <v>545</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226652</t>
+          <t xml:space="preserve">311234531</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-03-16</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8922221</t>
+          <t xml:space="preserve">5068289</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F132">
-        <v>1075</v>
+        <v>871</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226585</t>
+          <t xml:space="preserve">311234531</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-03-16</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681221</t>
+          <t xml:space="preserve">5068289</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F133">
-        <v>2283</v>
+        <v>582</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226923</t>
+          <t xml:space="preserve">311234531</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-07</t>
+          <t xml:space="preserve">2027-03-16</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5066243</t>
+          <t xml:space="preserve">5681141</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>731</v>
+        <v>2518</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227488</t>
+          <t xml:space="preserve">311237037</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677321</t>
+          <t xml:space="preserve">5065053</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F135">
-        <v>660</v>
+        <v>733</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227481</t>
+          <t xml:space="preserve">311239997</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-04-08</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677649</t>
+          <t xml:space="preserve">4385687</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>832</v>
+        <v>761</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227482</t>
+          <t xml:space="preserve">311243461</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682777</t>
+          <t xml:space="preserve">4385687</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F137">
-        <v>299</v>
+        <v>427</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227491</t>
+          <t xml:space="preserve">311243461</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682777</t>
+          <t xml:space="preserve">4385687</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F138">
-        <v>410</v>
+        <v>920</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227491</t>
+          <t xml:space="preserve">311243461</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682777</t>
+          <t xml:space="preserve">5065053</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>401</v>
+        <v>316</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227491</t>
+          <t xml:space="preserve">311244655</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682777</t>
+          <t xml:space="preserve">5065053</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F140">
-        <v>585</v>
+        <v>706</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227491</t>
+          <t xml:space="preserve">311244655</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681107</t>
+          <t xml:space="preserve">100019976</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7040,16 +7040,16 @@
         </is>
       </c>
       <c r="F141">
-        <v>1471</v>
+        <v>1159</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230458</t>
+          <t xml:space="preserve">311251933</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5068289</t>
+          <t xml:space="preserve">5069280</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F142">
-        <v>545</v>
+        <v>1526</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234531</t>
+          <t xml:space="preserve">311253167</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-16</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5068289</t>
+          <t xml:space="preserve">5685856</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
-        <v>871</v>
+        <v>2772</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234531</t>
+          <t xml:space="preserve">311261359</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-16</t>
+          <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5068289</t>
+          <t xml:space="preserve">5685856</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F144">
-        <v>582</v>
+        <v>958</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234531</t>
+          <t xml:space="preserve">311261359</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-16</t>
+          <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681141</t>
+          <t xml:space="preserve">8052360</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,16 +7240,16 @@
         </is>
       </c>
       <c r="F145">
-        <v>2518</v>
+        <v>2614</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237037</t>
+          <t xml:space="preserve">311261486</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4385687</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F146">
-        <v>761</v>
+        <v>4502</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243461</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4385687</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>427</v>
+        <v>845</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243461</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4385687</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F148">
-        <v>920</v>
+        <v>1172</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243461</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5063498</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F149">
-        <v>1793</v>
+        <v>489</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243467</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5063498</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F150">
-        <v>1224</v>
+        <v>1430</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243467</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5063498</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F151">
-        <v>1141</v>
+        <v>1163</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243467</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065053</t>
+          <t xml:space="preserve">5024077</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F152">
-        <v>316</v>
+        <v>1067</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244655</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-02</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065053</t>
+          <t xml:space="preserve">5071547</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>706</v>
+        <v>517</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244655</t>
+          <t xml:space="preserve">311268079</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-02</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019976</t>
+          <t xml:space="preserve">5686790</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>1159</v>
+        <v>1060</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251933</t>
+          <t xml:space="preserve">311268077</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069280</t>
+          <t xml:space="preserve">5675390</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F155">
-        <v>1526</v>
+        <v>3556</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253167</t>
+          <t xml:space="preserve">311268675</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-08-25</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5685856</t>
+          <t xml:space="preserve">8102701</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="F156">
-        <v>2772</v>
+        <v>7811</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261359</t>
+          <t xml:space="preserve">311275950</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5685856</t>
+          <t xml:space="preserve">5677384</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>958</v>
+        <v>3680</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261359</t>
+          <t xml:space="preserve">311276454</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">8052360</t>
+          <t xml:space="preserve">5677384</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F158">
-        <v>2614</v>
+        <v>316</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261488</t>
+          <t xml:space="preserve">311276454</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">5677384</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F159">
-        <v>4502</v>
+        <v>505</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311276454</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">100063457</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F160">
-        <v>845</v>
+        <v>8840</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311285829</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">9364746</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F161">
-        <v>1430</v>
+        <v>2596</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311293513</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">9479221</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>1163</v>
+        <v>2082</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311293514</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5024077</t>
+          <t xml:space="preserve">9479221</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F163">
-        <v>1067</v>
+        <v>326</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311293514</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5071547</t>
+          <t xml:space="preserve">9479221</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F164">
-        <v>517</v>
+        <v>3378</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268079</t>
+          <t xml:space="preserve">311293514</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5686790</t>
+          <t xml:space="preserve">9479221</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F165">
-        <v>1060</v>
+        <v>505</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268077</t>
+          <t xml:space="preserve">311293514</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675390</t>
+          <t xml:space="preserve">9925506</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>3556</v>
+        <v>2846</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268675</t>
+          <t xml:space="preserve">311293512</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-25</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8102701</t>
+          <t xml:space="preserve">9925506</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F167">
-        <v>7811</v>
+        <v>491</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275950</t>
+          <t xml:space="preserve">311293512</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677384</t>
+          <t xml:space="preserve">9925506</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F168">
-        <v>3680</v>
+        <v>1356</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276454</t>
+          <t xml:space="preserve">311293512</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677384</t>
+          <t xml:space="preserve">9413750</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F169">
-        <v>316</v>
+        <v>260</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276454</t>
+          <t xml:space="preserve">311299180</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677384</t>
+          <t xml:space="preserve">9413750</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F170">
-        <v>505</v>
+        <v>1443</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276454</t>
+          <t xml:space="preserve">311299180</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761664</t>
+          <t xml:space="preserve">9413750</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F171">
-        <v>2239</v>
+        <v>333</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276856</t>
+          <t xml:space="preserve">311299180</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063457</t>
+          <t xml:space="preserve">9413750</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F172">
-        <v>8840</v>
+        <v>5078</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285829</t>
+          <t xml:space="preserve">311299180</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">4386930</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F173">
-        <v>713</v>
+        <v>486</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290540</t>
+          <t xml:space="preserve">311302146</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2028-03-12</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9364746</t>
+          <t xml:space="preserve">5676524</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>2596</v>
+        <v>1339</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293513</t>
+          <t xml:space="preserve">311302517</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-13</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9479221</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F175">
-        <v>2082</v>
+        <v>1473</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293514</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9479221</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F176">
-        <v>326</v>
+        <v>1247</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293514</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9479221</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F177">
-        <v>3378</v>
+        <v>409</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293514</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9479221</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F178">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293514</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9925506</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F179">
-        <v>2846</v>
+        <v>539</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293512</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9925506</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F180">
-        <v>491</v>
+        <v>409</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293512</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9925506</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F181">
-        <v>1356</v>
+        <v>431</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293512</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-19</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413750</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F182">
-        <v>260</v>
+        <v>468</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299180</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413750</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F183">
-        <v>1443</v>
+        <v>713</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299180</t>
+          <t xml:space="preserve">311302895</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413750</t>
+          <t xml:space="preserve">738733, 7110243</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,16 +9190,16 @@
         </is>
       </c>
       <c r="F184">
-        <v>333</v>
+        <v>7097</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299180</t>
+          <t xml:space="preserve">311356047</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2029-01-23</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9413750</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>5078</v>
+        <v>1087</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299180</t>
+          <t xml:space="preserve">311360795</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386930</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F186">
-        <v>486</v>
+        <v>296</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302146</t>
+          <t xml:space="preserve">311360795</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-12</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5676524</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F187">
-        <v>1339</v>
+        <v>1820</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302517</t>
+          <t xml:space="preserve">311360795</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-13</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065055</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F188">
-        <v>2584</v>
+        <v>439</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302893</t>
+          <t xml:space="preserve">311360795</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-15</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8061999, 100756361</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F189">
-        <v>462</v>
+        <v>1964</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319559</t>
+          <t xml:space="preserve">311360795</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-10</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9486,11 +9486,11 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F190">
-        <v>1087</v>
+        <v>316</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">5023164</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F191">
-        <v>296</v>
+        <v>1424</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360795</t>
+          <t xml:space="preserve">311377399</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-05-16</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">5023164</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F192">
-        <v>1820</v>
+        <v>1452</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360795</t>
+          <t xml:space="preserve">311377399</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-05-16</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">5023164</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F193">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360795</t>
+          <t xml:space="preserve">311377399</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-05-16</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">5683897</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F194">
-        <v>1964</v>
+        <v>260</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360795</t>
+          <t xml:space="preserve">311377795</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-05-20</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">8761292</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F195">
-        <v>316</v>
+        <v>1170</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360795</t>
+          <t xml:space="preserve">311382807</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023164</t>
+          <t xml:space="preserve">8761292</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F196">
-        <v>1424</v>
+        <v>6435</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377399</t>
+          <t xml:space="preserve">311382807</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-16</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023164</t>
+          <t xml:space="preserve">8761292</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F197">
-        <v>1452</v>
+        <v>784</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377399</t>
+          <t xml:space="preserve">311382807</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-16</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023164</t>
+          <t xml:space="preserve">8761292</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F198">
-        <v>406</v>
+        <v>495</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377399</t>
+          <t xml:space="preserve">311382809</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-16</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5683897</t>
+          <t xml:space="preserve">8761292</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F199">
-        <v>260</v>
+        <v>635</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377795</t>
+          <t xml:space="preserve">311382807</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-20</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761292</t>
+          <t xml:space="preserve">5684787</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9990,16 +9990,16 @@
         </is>
       </c>
       <c r="F200">
-        <v>1170</v>
+        <v>3549</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382807</t>
+          <t xml:space="preserve">311429471</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2030-03-23</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761292</t>
+          <t xml:space="preserve">8061999, 100756361</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F201">
-        <v>6435</v>
+        <v>462</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382807</t>
+          <t xml:space="preserve">311523221</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2031-05-27</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,25 +10081,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761292</t>
+          <t xml:space="preserve">5065055</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F202">
-        <v>784</v>
+        <v>2584</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382807</t>
+          <t xml:space="preserve">311526974</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2031-06-10</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761292</t>
+          <t xml:space="preserve">5681894</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10140,16 +10140,16 @@
         </is>
       </c>
       <c r="F203">
-        <v>495</v>
+        <v>658</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382809</t>
+          <t xml:space="preserve">311531544</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761292</t>
+          <t xml:space="preserve">5683353</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F204">
-        <v>635</v>
+        <v>490</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382807</t>
+          <t xml:space="preserve">311542886</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2031-08-24</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5684787</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F205">
-        <v>3549</v>
+        <v>1920</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311429471</t>
+          <t xml:space="preserve">311543745</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-23</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">100193487, 100193488</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F206">
-        <v>6126</v>
+        <v>1081</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311460655</t>
+          <t xml:space="preserve">311544509</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-12</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681894</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F207">
-        <v>658</v>
+        <v>1211</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531544</t>
+          <t xml:space="preserve">311544504</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,25 +10381,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5683353</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F208">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542886</t>
+          <t xml:space="preserve">311544504</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-24</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963331</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F209">
-        <v>904</v>
+        <v>1300</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542864</t>
+          <t xml:space="preserve">311545073</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-24</t>
+          <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,25 +10481,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963331</t>
+          <t xml:space="preserve">100060559</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F210">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542864</t>
+          <t xml:space="preserve">311545304</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-24</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">738521, 8963331</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F211">
-        <v>1920</v>
+        <v>1873</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543745</t>
+          <t xml:space="preserve">311547108</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">8963331</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F212">
-        <v>1081</v>
+        <v>904</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544509</t>
+          <t xml:space="preserve">311547108</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">8963331</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F213">
-        <v>1211</v>
+        <v>2958</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544504</t>
+          <t xml:space="preserve">311547108</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">8963331</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F214">
-        <v>496</v>
+        <v>662</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544504</t>
+          <t xml:space="preserve">311547108</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">10102395</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F215">
-        <v>1300</v>
+        <v>869</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545073</t>
+          <t xml:space="preserve">311547768</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-01</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060559</t>
+          <t xml:space="preserve">5065055</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F216">
-        <v>676</v>
+        <v>2580</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545304</t>
+          <t xml:space="preserve">311547609</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,20 +10831,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102395</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F217">
-        <v>869</v>
+        <v>1123</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547770</t>
+          <t xml:space="preserve">311547755</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065055</t>
+          <t xml:space="preserve">10102395</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F218">
-        <v>2580</v>
+        <v>378</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547609</t>
+          <t xml:space="preserve">311547900</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">10102395</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F219">
-        <v>1123</v>
+        <v>431</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547755</t>
+          <t xml:space="preserve">311547900</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-13</t>
+          <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102395</t>
+          <t xml:space="preserve">5065053</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F220">
-        <v>378</v>
+        <v>664</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547900</t>
+          <t xml:space="preserve">311548472</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,25 +11031,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">10102395</t>
+          <t xml:space="preserve">5065055</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F221">
-        <v>431</v>
+        <v>551</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547900</t>
+          <t xml:space="preserve">311548471</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-14</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065053</t>
+          <t xml:space="preserve">5023164</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F222">
-        <v>664</v>
+        <v>290</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548472</t>
+          <t xml:space="preserve">311550941</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065055</t>
+          <t xml:space="preserve">7644732</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F223">
-        <v>551</v>
+        <v>4689</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548471</t>
+          <t xml:space="preserve">311551081</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,25 +11181,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023164</t>
+          <t xml:space="preserve">4384968</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F224">
-        <v>290</v>
+        <v>497</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311550941</t>
+          <t xml:space="preserve">311551440</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7644732</t>
+          <t xml:space="preserve">5027141</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11240,16 +11240,16 @@
         </is>
       </c>
       <c r="F225">
-        <v>4689</v>
+        <v>1999</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551081</t>
+          <t xml:space="preserve">311553916</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-10-08</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4384968</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F226">
-        <v>497</v>
+        <v>457</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551440</t>
+          <t xml:space="preserve">311556133</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-28</t>
+          <t xml:space="preserve">2031-10-19</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027141</t>
+          <t xml:space="preserve">9657620</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -11340,16 +11340,16 @@
         </is>
       </c>
       <c r="F227">
-        <v>1999</v>
+        <v>942</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311553916</t>
+          <t xml:space="preserve">311556478</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-08</t>
+          <t xml:space="preserve">2031-10-20</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">9657620</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F228">
-        <v>457</v>
+        <v>677</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556133</t>
+          <t xml:space="preserve">311559059</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11436,20 +11436,20 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F229">
-        <v>942</v>
+        <v>660</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556478</t>
+          <t xml:space="preserve">311559059</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-20</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11486,11 +11486,11 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F230">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -11536,11 +11536,11 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F231">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9657620</t>
+          <t xml:space="preserve">100048171</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F232">
-        <v>741</v>
+        <v>8318</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559059</t>
+          <t xml:space="preserve">311559708</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-11-04</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,25 +11631,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9657620</t>
+          <t xml:space="preserve">100014553</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F233">
-        <v>720</v>
+        <v>864</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559059</t>
+          <t xml:space="preserve">311561822</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048171</t>
+          <t xml:space="preserve">100014553</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F234">
-        <v>8318</v>
+        <v>796</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559708</t>
+          <t xml:space="preserve">311561822</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-04</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11731,20 +11731,20 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">100014553</t>
+          <t xml:space="preserve">5681894</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F235">
-        <v>864</v>
+        <v>481</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561824</t>
+          <t xml:space="preserve">311561835</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -11781,25 +11781,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">100014553</t>
+          <t xml:space="preserve">100068067</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F236">
-        <v>796</v>
+        <v>1707</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561826</t>
+          <t xml:space="preserve">311562445</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-11-17</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11831,25 +11831,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681894</t>
+          <t xml:space="preserve">5069280</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F237">
-        <v>481</v>
+        <v>3162</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561835</t>
+          <t xml:space="preserve">311564456</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-11-26</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">100068067</t>
+          <t xml:space="preserve">100047631</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F238">
-        <v>1707</v>
+        <v>1795</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562445</t>
+          <t xml:space="preserve">311565866</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-17</t>
+          <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069280</t>
+          <t xml:space="preserve">100047631</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F239">
-        <v>3162</v>
+        <v>1752</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564456</t>
+          <t xml:space="preserve">311565866</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-26</t>
+          <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11986,11 +11986,11 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F240">
-        <v>1795</v>
+        <v>1651</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -12036,11 +12036,11 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F241">
-        <v>1752</v>
+        <v>2003</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -12086,11 +12086,11 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F242">
-        <v>1651</v>
+        <v>3036</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -12131,25 +12131,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047631</t>
+          <t xml:space="preserve">5069728</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F243">
-        <v>2003</v>
+        <v>307</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565866</t>
+          <t xml:space="preserve">311596888</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-02</t>
+          <t xml:space="preserve">2032-05-02</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,25 +12181,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047631</t>
+          <t xml:space="preserve">4386930</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F244">
-        <v>3036</v>
+        <v>3891</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565866</t>
+          <t xml:space="preserve">311599447</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-02</t>
+          <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069728</t>
+          <t xml:space="preserve">5686374</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12240,16 +12240,16 @@
         </is>
       </c>
       <c r="F245">
-        <v>307</v>
+        <v>415</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596888</t>
+          <t xml:space="preserve">311600372</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-02</t>
+          <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386930</t>
+          <t xml:space="preserve">4383004</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -12290,16 +12290,16 @@
         </is>
       </c>
       <c r="F246">
-        <v>3891</v>
+        <v>1044</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599447</t>
+          <t xml:space="preserve">311601087</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-10</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5686374</t>
+          <t xml:space="preserve">5023678</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -12340,16 +12340,16 @@
         </is>
       </c>
       <c r="F247">
-        <v>415</v>
+        <v>272</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600372</t>
+          <t xml:space="preserve">311601091</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-16</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4383004</t>
+          <t xml:space="preserve">4383225</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F248">
-        <v>1044</v>
+        <v>475</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601114</t>
+          <t xml:space="preserve">311601582</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023678</t>
+          <t xml:space="preserve">7730833</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -12440,16 +12440,16 @@
         </is>
       </c>
       <c r="F249">
-        <v>272</v>
+        <v>1930</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601091</t>
+          <t xml:space="preserve">311602713</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12481,25 +12481,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4383225</t>
+          <t xml:space="preserve">5170795</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F250">
-        <v>475</v>
+        <v>387</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601582</t>
+          <t xml:space="preserve">311607088</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-06-13</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12531,25 +12531,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730833</t>
+          <t xml:space="preserve">5029957</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F251">
-        <v>1930</v>
+        <v>1346</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602713</t>
+          <t xml:space="preserve">311608425</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-24</t>
+          <t xml:space="preserve">2032-06-16</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170795</t>
+          <t xml:space="preserve">5065703</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -12590,16 +12590,16 @@
         </is>
       </c>
       <c r="F252">
-        <v>387</v>
+        <v>773</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607088</t>
+          <t xml:space="preserve">311608421</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-13</t>
+          <t xml:space="preserve">2032-06-16</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12631,25 +12631,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5029957</t>
+          <t xml:space="preserve">5063722</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F253">
-        <v>1346</v>
+        <v>283</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608425</t>
+          <t xml:space="preserve">311609001</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-16</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065703</t>
+          <t xml:space="preserve">8963331</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -12690,16 +12690,16 @@
         </is>
       </c>
       <c r="F254">
-        <v>773</v>
+        <v>365</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608421</t>
+          <t xml:space="preserve">311609437</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-16</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12731,25 +12731,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5063722</t>
+          <t xml:space="preserve">5029957</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F255">
-        <v>283</v>
+        <v>738</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609001</t>
+          <t xml:space="preserve">311611358</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963331</t>
+          <t xml:space="preserve">8761494</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -12790,16 +12790,16 @@
         </is>
       </c>
       <c r="F256">
-        <v>365</v>
+        <v>663</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609437</t>
+          <t xml:space="preserve">311612612</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12831,25 +12831,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5029957</t>
+          <t xml:space="preserve">5065422</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F257">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611358</t>
+          <t xml:space="preserve">311618649</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-08-04</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761494</t>
+          <t xml:space="preserve">4383418</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -12890,16 +12890,16 @@
         </is>
       </c>
       <c r="F258">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612612</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-04</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12931,25 +12931,25 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065422</t>
+          <t xml:space="preserve">4383418</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F259">
-        <v>743</v>
+        <v>639</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618649</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-04</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -12986,20 +12986,20 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F260">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623572</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-27</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -13036,20 +13036,20 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F261">
-        <v>639</v>
+        <v>996</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624915</t>
+          <t xml:space="preserve">311626810</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -13086,20 +13086,20 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F262">
-        <v>616</v>
+        <v>676</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625696</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-06</t>
+          <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -13131,25 +13131,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">4383418</t>
+          <t xml:space="preserve">5071711</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F263">
-        <v>676</v>
+        <v>2126</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625698</t>
+          <t xml:space="preserve">311629200</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-06</t>
+          <t xml:space="preserve">2032-09-20</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4383418</t>
+          <t xml:space="preserve">4382310</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F264">
-        <v>996</v>
+        <v>540</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626810</t>
+          <t xml:space="preserve">311634147</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-09</t>
+          <t xml:space="preserve">2032-10-07</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5071711</t>
+          <t xml:space="preserve">5682516</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -13240,16 +13240,16 @@
         </is>
       </c>
       <c r="F265">
-        <v>2126</v>
+        <v>898</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629202</t>
+          <t xml:space="preserve">311638500</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-20</t>
+          <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382310</t>
+          <t xml:space="preserve">4388967</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F266">
-        <v>540</v>
+        <v>891</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311634147</t>
+          <t xml:space="preserve">311641897</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-07</t>
+          <t xml:space="preserve">2032-11-10</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -13331,25 +13331,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682516</t>
+          <t xml:space="preserve">5069651</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F267">
-        <v>898</v>
+        <v>447</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311638500</t>
+          <t xml:space="preserve">311646320</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-27</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -13381,25 +13381,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4388967</t>
+          <t xml:space="preserve">4388846</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F268">
-        <v>891</v>
+        <v>792</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641897</t>
+          <t xml:space="preserve">311648159</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-10</t>
+          <t xml:space="preserve">2032-12-09</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -13431,25 +13431,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069651</t>
+          <t xml:space="preserve">8761674</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F269">
-        <v>447</v>
+        <v>888</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646320</t>
+          <t xml:space="preserve">311687079</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4388846</t>
+          <t xml:space="preserve">9486503</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -13490,16 +13490,16 @@
         </is>
       </c>
       <c r="F270">
-        <v>792</v>
+        <v>310</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648159</t>
+          <t xml:space="preserve">311697547</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-09</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -13531,25 +13531,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">314810</t>
+          <t xml:space="preserve">9486503</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F271">
-        <v>476</v>
+        <v>1066</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680347</t>
+          <t xml:space="preserve">311697547</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -13581,25 +13581,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761674</t>
+          <t xml:space="preserve">9817903</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F272">
-        <v>888</v>
+        <v>1155</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311687079</t>
+          <t xml:space="preserve">311697549</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-12</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">323176, 323177, 323178</t>
+          <t xml:space="preserve">5767043</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -13640,16 +13640,16 @@
         </is>
       </c>
       <c r="F273">
-        <v>4203</v>
+        <v>388</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688483</t>
+          <t xml:space="preserve">311700558</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-16</t>
+          <t xml:space="preserve">2033-08-16</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -13681,25 +13681,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9486503</t>
+          <t xml:space="preserve">5767043</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F274">
-        <v>310</v>
+        <v>447</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697547</t>
+          <t xml:space="preserve">311700558</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2033-08-16</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -13731,25 +13731,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9486503</t>
+          <t xml:space="preserve">7719900</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F275">
-        <v>1066</v>
+        <v>496</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697547</t>
+          <t xml:space="preserve">311701570</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">9817903</t>
+          <t xml:space="preserve">5063498</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -13790,16 +13790,16 @@
         </is>
       </c>
       <c r="F276">
-        <v>1155</v>
+        <v>1793</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697549</t>
+          <t xml:space="preserve">311704413</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -13831,25 +13831,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">315765</t>
+          <t xml:space="preserve">5063498</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F277">
-        <v>355</v>
+        <v>1224</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698053</t>
+          <t xml:space="preserve">311704413</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -13881,25 +13881,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5767043</t>
+          <t xml:space="preserve">5063498</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F278">
-        <v>388</v>
+        <v>1141</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700558</t>
+          <t xml:space="preserve">311704413</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-16</t>
+          <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -13931,25 +13931,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5767043</t>
+          <t xml:space="preserve">5028976</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F279">
-        <v>447</v>
+        <v>365</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700558</t>
+          <t xml:space="preserve">311707159</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-16</t>
+          <t xml:space="preserve">2033-09-13</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -13981,25 +13981,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">7719900</t>
+          <t xml:space="preserve">9244056</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F280">
-        <v>496</v>
+        <v>340</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701570</t>
+          <t xml:space="preserve">311708791</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">322724, 322725</t>
+          <t xml:space="preserve">5029957</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -14040,16 +14040,16 @@
         </is>
       </c>
       <c r="F281">
-        <v>1159</v>
+        <v>3426</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707170</t>
+          <t xml:space="preserve">311711744</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-13</t>
+          <t xml:space="preserve">2033-10-02</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14081,25 +14081,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5028976</t>
+          <t xml:space="preserve">5029957</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F282">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707159</t>
+          <t xml:space="preserve">311711744</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-13</t>
+          <t xml:space="preserve">2033-10-02</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -14131,25 +14131,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">9244056</t>
+          <t xml:space="preserve">5063888</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F283">
-        <v>340</v>
+        <v>636</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708791</t>
+          <t xml:space="preserve">311719140</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-19</t>
+          <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -14181,25 +14181,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5029957</t>
+          <t xml:space="preserve">5065055</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F284">
-        <v>3426</v>
+        <v>287</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711744</t>
+          <t xml:space="preserve">311719139</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-02</t>
+          <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -14231,25 +14231,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5029957</t>
+          <t xml:space="preserve">5686174</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F285">
-        <v>421</v>
+        <v>2822</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711744</t>
+          <t xml:space="preserve">311719126</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-02</t>
+          <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -14281,20 +14281,20 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5063888</t>
+          <t xml:space="preserve">5686174</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F286">
-        <v>636</v>
+        <v>512</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719140</t>
+          <t xml:space="preserve">311719126</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -14331,25 +14331,25 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5065055</t>
+          <t xml:space="preserve">5027227</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F287">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719139</t>
+          <t xml:space="preserve">311721665</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-01</t>
+          <t xml:space="preserve">2033-11-13</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5686174</t>
+          <t xml:space="preserve">10056356</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -14390,16 +14390,16 @@
         </is>
       </c>
       <c r="F288">
-        <v>2822</v>
+        <v>2676</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719126</t>
+          <t xml:space="preserve">311722342</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-01</t>
+          <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -14431,25 +14431,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5686174</t>
+          <t xml:space="preserve">5677396</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F289">
-        <v>512</v>
+        <v>930</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719126</t>
+          <t xml:space="preserve">311722268</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-01</t>
+          <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -14481,25 +14481,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027227</t>
+          <t xml:space="preserve">8290216</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F290">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721665</t>
+          <t xml:space="preserve">311722263</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-13</t>
+          <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">10056356</t>
+          <t xml:space="preserve">8761664</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -14540,11 +14540,11 @@
         </is>
       </c>
       <c r="F291">
-        <v>2676</v>
+        <v>2239</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722342</t>
+          <t xml:space="preserve">311722265</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677396</t>
+          <t xml:space="preserve">5025876</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -14590,16 +14590,16 @@
         </is>
       </c>
       <c r="F292">
-        <v>930</v>
+        <v>468</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722268</t>
+          <t xml:space="preserve">311725489</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-15</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">8290216</t>
+          <t xml:space="preserve">5026182</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -14640,16 +14640,16 @@
         </is>
       </c>
       <c r="F293">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722263</t>
+          <t xml:space="preserve">311725587</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-15</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -14681,25 +14681,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">320650, 320651, 320652</t>
+          <t xml:space="preserve">4388119, 100596459</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F294">
-        <v>2140</v>
+        <v>2389</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725165</t>
+          <t xml:space="preserve">311738925</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-28</t>
+          <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5025876</t>
+          <t xml:space="preserve">5678422</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -14740,16 +14740,16 @@
         </is>
       </c>
       <c r="F295">
-        <v>468</v>
+        <v>724</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725489</t>
+          <t xml:space="preserve">311744902</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-03-13</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5026182</t>
+          <t xml:space="preserve">7110243</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -14790,16 +14790,16 @@
         </is>
       </c>
       <c r="F296">
-        <v>398</v>
+        <v>1164</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725587</t>
+          <t xml:space="preserve">311754990</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-04-26</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">4388119, 100596459</t>
+          <t xml:space="preserve">5677357</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F297">
-        <v>2389</v>
+        <v>3915</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738925</t>
+          <t xml:space="preserve">311758725</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-14</t>
+          <t xml:space="preserve">2034-05-13</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5678422</t>
+          <t xml:space="preserve">5687223</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -14890,16 +14890,16 @@
         </is>
       </c>
       <c r="F298">
-        <v>724</v>
+        <v>3892</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744902</t>
+          <t xml:space="preserve">311763305</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-13</t>
+          <t xml:space="preserve">2034-05-31</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -14931,25 +14931,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110243</t>
+          <t xml:space="preserve">5677324</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F299">
-        <v>1164</v>
+        <v>620</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311754990</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-26</t>
+          <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -14981,25 +14981,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">5677357</t>
+          <t xml:space="preserve">5677324</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F300">
-        <v>3915</v>
+        <v>514</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758725</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-13</t>
+          <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -15031,25 +15031,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5687223</t>
+          <t xml:space="preserve">5677324</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F301">
-        <v>3892</v>
+        <v>1343</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763305</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-31</t>
+          <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -15086,15 +15086,15 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F302">
-        <v>620</v>
+        <v>415</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769952</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -15136,15 +15136,15 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F303">
-        <v>514</v>
+        <v>387</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769954</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -15186,15 +15186,15 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F304">
-        <v>387</v>
+        <v>1105</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769953</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -15231,25 +15231,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5677324</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F305">
-        <v>252</v>
+        <v>968</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777446</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-12</t>
+          <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -15281,25 +15281,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7841251, 100756360</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F306">
-        <v>252</v>
+        <v>1749</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777446</t>
+          <t xml:space="preserve">311776569</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-12</t>
+          <t xml:space="preserve">2034-08-06</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -15336,20 +15336,20 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F307">
-        <v>1613</v>
+        <v>252</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311777446</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-08-12</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -15386,20 +15386,20 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F308">
-        <v>486</v>
+        <v>252</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311777446</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-08-12</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -15436,11 +15436,11 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F309">
-        <v>540</v>
+        <v>1613</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -15486,11 +15486,11 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F310">
-        <v>428</v>
+        <v>486</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -15536,11 +15536,11 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F311">
-        <v>2260</v>
+        <v>540</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -15586,11 +15586,11 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F312">
-        <v>1303</v>
+        <v>428</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -15636,11 +15636,11 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F313">
-        <v>253</v>
+        <v>2260</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -15686,11 +15686,11 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F314">
-        <v>562</v>
+        <v>1303</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -15736,11 +15736,11 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F315">
-        <v>2917</v>
+        <v>253</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -15786,11 +15786,11 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F316">
-        <v>505</v>
+        <v>562</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -15836,11 +15836,11 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F317">
-        <v>380</v>
+        <v>2917</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -15881,25 +15881,25 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023541</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F318">
-        <v>1328</v>
+        <v>505</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787606</t>
+          <t xml:space="preserve">311781557</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -15931,25 +15931,25 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027423</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F319">
-        <v>4461</v>
+        <v>380</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818310</t>
+          <t xml:space="preserve">311781557</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -15981,25 +15981,25 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">7524697</t>
+          <t xml:space="preserve">5023541</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F320">
-        <v>825</v>
+        <v>1328</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820661</t>
+          <t xml:space="preserve">311787606</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-27</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">5027423</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -16040,16 +16040,16 @@
         </is>
       </c>
       <c r="F321">
-        <v>542</v>
+        <v>4461</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823954</t>
+          <t xml:space="preserve">311818307</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -16081,25 +16081,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">7524697</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F322">
-        <v>1337</v>
+        <v>825</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824146</t>
+          <t xml:space="preserve">311820661</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -16136,15 +16136,15 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F323">
-        <v>742</v>
+        <v>542</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824146</t>
+          <t xml:space="preserve">311823954</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -16181,25 +16181,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387067</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F324">
-        <v>320</v>
+        <v>1337</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824278</t>
+          <t xml:space="preserve">311824146</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -16231,25 +16231,25 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681097</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F325">
-        <v>1766</v>
+        <v>742</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826212</t>
+          <t xml:space="preserve">311824146</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-22</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -16281,25 +16281,25 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681097</t>
+          <t xml:space="preserve">4387067</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F326">
-        <v>982</v>
+        <v>320</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826209</t>
+          <t xml:space="preserve">311824278</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-22</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5681097</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -16340,16 +16340,16 @@
         </is>
       </c>
       <c r="F327">
-        <v>2848</v>
+        <v>1766</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311826212</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -16381,25 +16381,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5681097</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F328">
-        <v>1172</v>
+        <v>982</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311826209</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -16436,15 +16436,15 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F329">
-        <v>2017</v>
+        <v>2848</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -16486,15 +16486,15 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F330">
-        <v>371</v>
+        <v>1172</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826639</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -16536,15 +16536,15 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F331">
-        <v>803</v>
+        <v>2017</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -16581,25 +16581,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069465</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F332">
-        <v>1387</v>
+        <v>371</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827156</t>
+          <t xml:space="preserve">311826639</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -16631,25 +16631,25 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069995</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F333">
-        <v>5886</v>
+        <v>803</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828899</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-02</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">5069465</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -16690,16 +16690,16 @@
         </is>
       </c>
       <c r="F334">
-        <v>361</v>
+        <v>1387</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311827156</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">5069995</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -16740,16 +16740,16 @@
         </is>
       </c>
       <c r="F335">
-        <v>525</v>
+        <v>5886</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311828899</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-05-02</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218207</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -16790,11 +16790,11 @@
         </is>
       </c>
       <c r="F336">
-        <v>5961</v>
+        <v>361</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832620</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -16831,25 +16831,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">5028587</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F337">
-        <v>3079</v>
+        <v>525</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833037</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -16881,25 +16881,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">10170544</t>
+          <t xml:space="preserve">9218207</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F338">
-        <v>636</v>
+        <v>5961</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834137</t>
+          <t xml:space="preserve">311832620</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-25</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -16931,25 +16931,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">100068900</t>
+          <t xml:space="preserve">5028587</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F339">
-        <v>1983</v>
+        <v>3079</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837586</t>
+          <t xml:space="preserve">311833037</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-12</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -16981,25 +16981,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761653</t>
+          <t xml:space="preserve">10170544</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F340">
-        <v>4121</v>
+        <v>636</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839051</t>
+          <t xml:space="preserve">311834137</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-05-25</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761653</t>
+          <t xml:space="preserve">100068900</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -17040,16 +17040,16 @@
         </is>
       </c>
       <c r="F341">
-        <v>1713</v>
+        <v>1983</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839054</t>
+          <t xml:space="preserve">311837586</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">304880, 304881</t>
+          <t xml:space="preserve">8761653</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -17090,16 +17090,16 @@
         </is>
       </c>
       <c r="F342">
-        <v>2656</v>
+        <v>4121</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841720</t>
+          <t xml:space="preserve">311839051</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-30</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -17131,25 +17131,25 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675450</t>
+          <t xml:space="preserve">8761653</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F343">
-        <v>2112</v>
+        <v>1713</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844296</t>
+          <t xml:space="preserve">311839054</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-11</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766969</t>
+          <t xml:space="preserve">5675450</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -17190,16 +17190,16 @@
         </is>
       </c>
       <c r="F344">
-        <v>2092</v>
+        <v>2112</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847624</t>
+          <t xml:space="preserve">311844296</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-06</t>
+          <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">100497241</t>
+          <t xml:space="preserve">5766969</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -17240,16 +17240,16 @@
         </is>
       </c>
       <c r="F345">
-        <v>1865</v>
+        <v>2092</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861662</t>
+          <t xml:space="preserve">311847624</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-13</t>
+          <t xml:space="preserve">2035-08-06</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">100643290</t>
+          <t xml:space="preserve">100497241</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -17290,16 +17290,16 @@
         </is>
       </c>
       <c r="F346">
-        <v>711</v>
+        <v>1865</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869504</t>
+          <t xml:space="preserve">311861662</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2035-10-13</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -17336,15 +17336,15 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F347">
-        <v>307</v>
+        <v>711</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869505</t>
+          <t xml:space="preserve">311869504</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -17381,25 +17381,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">100891244, 100891245</t>
+          <t xml:space="preserve">100643290</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F348">
-        <v>5997</v>
+        <v>307</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871668</t>
+          <t xml:space="preserve">311869505</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">

--- a/public/exports/29189897.xlsx
+++ b/public/exports/29189897.xlsx
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210846</t>
+          <t xml:space="preserve">311210802</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261488</t>
+          <t xml:space="preserve">311261486</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629202</t>
+          <t xml:space="preserve">311629200</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769952</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818310</t>
+          <t xml:space="preserve">311818307</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824278</t>
+          <t xml:space="preserve">311824280</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -19674,7 +19674,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">

--- a/public/exports/29189897.xlsx
+++ b/public/exports/29189897.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L348"/>
+  <dimension ref="A1:M348"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S (Kolding)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-08</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-01-24</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-12-22</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-02-05</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-02-05</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rigenstrup</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rigenstrup</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rigenstrup</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-09</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Total-Tjek</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-18</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-04</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bartnik Byg</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-03</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-02</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Neo Energi I/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-09</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-07</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-16</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-16</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-16</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-08</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-02</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-25</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-19</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-12</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-13</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-23</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-16</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-16</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-16</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Neo Energi I/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-20</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-23</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">NiH Energy ApS</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-12</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-27</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-10</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-24</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-01</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12594,20 +13639,25 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547770</t>
+          <t xml:space="preserve">311547768</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-13</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-14</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-28</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-08</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-19</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-20</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-04</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-17</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-26</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-02</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-02</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-10</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14394,20 +15589,25 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601114</t>
+          <t xml:space="preserve">311601087</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-24</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-13</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-16</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-16</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-04</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15054,20 +16304,25 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626813</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15114,20 +16369,25 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626813</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15234,20 +16499,25 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626813</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15294,20 +16564,25 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626813</t>
+          <t xml:space="preserve">311626812</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-09</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-20</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-07</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-10</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-09</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-16</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,15 +17219,20 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-16</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-16</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,15 +17674,20 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-13</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-13</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-02</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-02</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-01</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-13</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17159,15 +18584,20 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17219,15 +18649,20 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17339,15 +18779,20 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17399,15 +18844,20 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-13</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-26</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-13</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-31</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17819,15 +19299,20 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17879,15 +19364,20 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17934,20 +19424,25 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769954</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17999,15 +19494,20 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18054,20 +19554,25 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769953</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18119,15 +19624,20 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18179,15 +19689,20 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-28</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18239,15 +19754,20 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-06</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18299,15 +19819,20 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-12</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18359,15 +19884,20 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-12</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18419,15 +19949,20 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18479,15 +20014,20 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18539,15 +20079,20 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18599,15 +20144,20 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18659,15 +20209,20 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18719,15 +20274,20 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18779,15 +20339,20 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18839,15 +20404,20 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18899,15 +20469,20 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18959,15 +20534,20 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19019,15 +20599,20 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-30</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19079,15 +20664,20 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19139,15 +20729,20 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19199,15 +20794,20 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19259,15 +20859,20 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19319,15 +20924,20 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19379,15 +20989,20 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19434,20 +21049,25 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824280</t>
+          <t xml:space="preserve">311824278</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19499,15 +21119,20 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19559,15 +21184,20 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19619,15 +21249,20 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19679,15 +21314,20 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19739,15 +21379,20 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19799,15 +21444,20 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19859,15 +21509,20 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19919,15 +21574,20 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19979,15 +21639,20 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-02</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20039,15 +21704,20 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20099,15 +21769,20 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20159,15 +21834,20 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20219,15 +21899,20 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20279,15 +21964,20 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-25</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20339,15 +22029,20 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20399,15 +22094,20 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20459,15 +22159,20 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20519,15 +22224,20 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-30</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20579,15 +22289,20 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20639,15 +22354,20 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-06</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20699,15 +22419,20 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-13</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20759,15 +22484,20 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20819,15 +22549,20 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20879,21 +22614,26 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L348" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L348"/>
+  <autoFilter ref="A1:M348"/>
 </worksheet>
 </file>
--- a/public/exports/29189897.xlsx
+++ b/public/exports/29189897.xlsx
@@ -8959,7 +8959,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267712</t>
+          <t xml:space="preserve">311267710</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561824</t>
+          <t xml:space="preserve">311561822</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561826</t>
+          <t xml:space="preserve">311561822</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
